--- a/docs/指摘.xlsx
+++ b/docs/指摘.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ff14-submarine\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E55297-C06A-43DC-A250-4B53E19DEC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5E10EF-F4D8-4415-A117-96B2207BAB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="4620" windowWidth="43200" windowHeight="17145" xr2:uid="{A9B00674-73A0-46FD-9C8F-FC0EB70029EE}"/>
+    <workbookView xWindow="3390" yWindow="4620" windowWidth="43200" windowHeight="17145" activeTab="1" xr2:uid="{A9B00674-73A0-46FD-9C8F-FC0EB70029EE}"/>
   </bookViews>
   <sheets>
-    <sheet name="1回め" sheetId="1" r:id="rId1"/>
+    <sheet name="1回目" sheetId="1" r:id="rId1"/>
+    <sheet name="2回目" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -758,6 +759,950 @@
           <a:endParaRPr lang="ja-JP" altLang="ja-JP">
             <a:effectLst/>
           </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>448982</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>219371</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A969F2E-67B2-A89D-2065-B8E4958DADE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="238125"/>
+          <a:ext cx="9364382" cy="2124371"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>219074</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152399</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD77DDE8-4AB8-44D8-8826-5CC83FC84518}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="219074" y="552450"/>
+          <a:ext cx="4048125" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61DC9AD9-2F75-4C7C-B44B-78743AB6C824}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4924425" y="1076325"/>
+          <a:ext cx="4333875" cy="1123950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="吹き出し: 四角形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED81BFE1-E884-143F-BAD5-98DAEEDF85D9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4867275" y="171450"/>
+          <a:ext cx="2695575" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -65709"/>
+            <a:gd name="adj2" fmla="val 86667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>高さがあっていない</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="矢印: 左右 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E16945E-EBC5-5B92-9476-2BE4D14C9846}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="1831782">
+          <a:off x="4162425" y="1190625"/>
+          <a:ext cx="800100" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="leftRightArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>448982</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>219371</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{029AE835-11BB-457E-BB58-19D5DC729AE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3529853"/>
+          <a:ext cx="9335247" cy="2101959"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>212912</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>224118</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>661147</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>212911</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="正方形/長方形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15655081-D034-4EC5-960E-7791681E4301}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="212912" y="3753971"/>
+          <a:ext cx="1815353" cy="1636058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123265</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>201706</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A751409-1924-48B6-80E9-43E5D53DACB1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2173941" y="3731559"/>
+          <a:ext cx="1815353" cy="1636058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>168087</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C07FD83-C960-474E-A369-19282DB8E599}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4784912" y="3709147"/>
+          <a:ext cx="4291853" cy="1636058"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>392206</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>344581</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>131669</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="吹き出し: 四角形 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{92646F26-3D21-499A-8A59-3E99168CB0E2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3810000" y="3238500"/>
+          <a:ext cx="2686610" cy="1128993"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -27753"/>
+            <a:gd name="adj2" fmla="val 101555"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>３つに分けて高さを揃えたら？</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>67235</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>373878</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>181897</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4188B94E-091B-6E5E-3E03-4D15F7B22EDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="67235" y="8180294"/>
+          <a:ext cx="9192908" cy="2591162"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>549087</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>501462</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>232522</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="吹き出し: 四角形 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D2622B4-4473-4648-91D0-BB0507D25BBC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9435352" y="7104529"/>
+          <a:ext cx="2686610" cy="1128993"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -56533"/>
+            <a:gd name="adj2" fmla="val 74756"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・潜水艦ランクと同じ指摘</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・艦橋の下のグリッドがない</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>・項目名のところ、グリッドで囲んだほうがよくない。コストの左側は不要</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>145676</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>201705</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>425822</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>145677</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA77BB57-4A1F-486A-931E-D880275BEEA4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="145676" y="8202705"/>
+          <a:ext cx="9166411" cy="2767854"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>302559</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>67234</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>134469</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>56029</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="フローチャート: 結合子 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A2EFEDB-A96D-EEAB-5C2C-74BBD00A2851}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2353235" y="8303558"/>
+          <a:ext cx="3249705" cy="459442"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartConnector">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>44823</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>647140</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>232522</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="吹き出し: 四角形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56AD5D01-D6A0-476E-99C2-F003A291E5FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4112559" y="6869205"/>
+          <a:ext cx="2686610" cy="1128993"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -56533"/>
+            <a:gd name="adj2" fmla="val 74756"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ここにグリッドは不要</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
         <a:p>
           <a:pPr algn="l"/>
@@ -1094,4 +2039,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A36A95-512D-47D3-8F7F-A0FA1EA4B02B}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" customFormat="1" x14ac:dyDescent="0.4"/>
+    <row r="2" customFormat="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/指摘.xlsx
+++ b/docs/指摘.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ff14-submarine\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D5E10EF-F4D8-4415-A117-96B2207BAB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F430A027-3F82-432C-9447-CD39A40522C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="4620" windowWidth="43200" windowHeight="17145" activeTab="1" xr2:uid="{A9B00674-73A0-46FD-9C8F-FC0EB70029EE}"/>
+    <workbookView xWindow="3390" yWindow="4620" windowWidth="43200" windowHeight="17145" activeTab="2" xr2:uid="{A9B00674-73A0-46FD-9C8F-FC0EB70029EE}"/>
   </bookViews>
   <sheets>
     <sheet name="1回目" sheetId="1" r:id="rId1"/>
     <sheet name="2回目" sheetId="2" r:id="rId2"/>
+    <sheet name="3回目" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1707,6 +1708,370 @@
         <a:p>
           <a:pPr algn="l"/>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>401350</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>152754</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A466E0D-78B0-EB29-DA7E-701948FAB6F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5000625"/>
+          <a:ext cx="9316750" cy="2534004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>641538</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>21290</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>428626</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>76199</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA490E4F-AD87-4A89-AB49-0A163C5A4F49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5442138" y="5021915"/>
+          <a:ext cx="3901888" cy="2436159"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>560</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>62193</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="吹き出し: 四角形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{30E7C273-3834-469F-8EC1-EBD6782CF90F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9658350" y="5362575"/>
+          <a:ext cx="2686610" cy="1128993"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -62852"/>
+            <a:gd name="adj2" fmla="val 7064"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>各項目の幅を固定長で揃えられない？</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+          </a:br>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>運が未選択のときだけ他の項目名と幅が違う</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>125087</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>114449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{709B064B-8960-B49D-EACD-B0E265CFA9EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="238125"/>
+          <a:ext cx="9040487" cy="1066949"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>228601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>82363</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>47626</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBC145C9-E16F-4A55-9BA6-197027CA2597}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5095875" y="228601"/>
+          <a:ext cx="3901888" cy="1009650"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>305360</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>81243</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="吹き出し: 四角形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{810BF893-1286-4367-9A5D-BBAF8524734F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9277350" y="381000"/>
+          <a:ext cx="2686610" cy="1128993"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -62852"/>
+            <a:gd name="adj2" fmla="val 7064"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>キャパシティだけ項目名が長く、他の項目名と釣り合っていない。項目の表示名はキャパでもｷｬﾊﾟでもよい</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2053,4 +2418,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08ED95B4-1AEF-4EB7-AEBF-1B1B2EA34794}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/指摘.xlsx
+++ b/docs/指摘.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ff14-submarine\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F430A027-3F82-432C-9447-CD39A40522C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47CCC285-1826-4A9B-B6A6-09C6DBF486CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="4620" windowWidth="43200" windowHeight="17145" activeTab="2" xr2:uid="{A9B00674-73A0-46FD-9C8F-FC0EB70029EE}"/>
+    <workbookView xWindow="3390" yWindow="4620" windowWidth="43200" windowHeight="17145" activeTab="3" xr2:uid="{A9B00674-73A0-46FD-9C8F-FC0EB70029EE}"/>
   </bookViews>
   <sheets>
     <sheet name="1回目" sheetId="1" r:id="rId1"/>
     <sheet name="2回目" sheetId="2" r:id="rId2"/>
     <sheet name="3回目" sheetId="3" r:id="rId3"/>
+    <sheet name="4回目" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2075,6 +2076,155 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>381532</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>95562</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4385D22-31FD-585E-7935-4273A10B67B1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="3810532" cy="2238687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6DA8442F-AEF8-ACCB-0DB5-E098388F6F77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="247650" y="304800"/>
+          <a:ext cx="9525" cy="1781175"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="直線コネクタ 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6632CEDF-237F-4880-8E57-073D4F45A427}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="247650" y="2047875"/>
+          <a:ext cx="3457575" cy="28575"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2429,4 +2579,15 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1594F8-2AC7-4198-BBC7-A0460BDAA7D3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>